--- a/data/regles_panel_fournisseurs.xlsx
+++ b/data/regles_panel_fournisseurs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DamienLauger\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DDBB3D-F4A7-4EFA-8572-C2D684972B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76E10F00-EA07-4E8C-B51C-CE10462B04D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fournisseurs Export" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fournisseurs Panel'!$A$1:$B$30</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="181">
   <si>
     <t>FICHIER FOURNISSEURS SALESFORCE - EXPORT SEGMENTS &amp; CRITÈRES</t>
   </si>
@@ -523,6 +536,125 @@
   </si>
   <si>
     <t>3/10 voir CréditSafe 30/100</t>
+  </si>
+  <si>
+    <t>Marge</t>
+  </si>
+  <si>
+    <t>Electricité  ou Gaz = 20€ / MWh</t>
+  </si>
+  <si>
+    <t>Electicité= Mail : 
+30 €/MWh
+Grilles : 
+marge intégrée dans les prix 15 €/MWh ou 8 €/MWh (cf. détails grilles) GAZ= Mail : 
+30 €/MWh
+Grilles : 
+marge intégrée dans les prix 10 €/MWh (cf. détails grilles)</t>
+  </si>
+  <si>
+    <t>Electricité= 
+C2 : 10 €/MWh
+C4/C5 : 20 €/MWh ) GAZ=
+&lt; 200 MWh : 24 €/MWh
+&lt; 300 MWh : 16 €/MWh
+&lt; 5 GWh : 8 €/MWh
+&lt; 8 GWh : 5 €/MWh</t>
+  </si>
+  <si>
+    <t>Electricité= 
+C1-C4 : 20 €/MWh
+C5 : 34 €/MWh ) GAZ= Mail : 
+MM/JJ (T4/T3/T2) : 20 €/MWh
+1M/6M (T2/T1) : 34 €/MWh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricité= Mail : 
+Marge max à déterminer pour contrat avec engagement (si &gt; 8 €/MWh pour Capitole alors valider avec Xavier)
+Grilles C5 :
+Pas de marge appliquée (CAR*2) </t>
+  </si>
+  <si>
+    <t>Electricité=
+50 MWh &lt; CAR &lt; 600 MWh : 30 €/MWh
+600 MWh &lt; CAR &lt; 1 GWh : 24 €/MWh
+&gt; 1 GWh : 20 €/MWh ) GAZ= 
+T2 : 15 €/MWh 
+T3 : 10 €/MWh</t>
+  </si>
+  <si>
+    <t>Gaz= 
+10 €/MWh pour Capitole (6 €/MWh pour SDC)
+Marge dans l'abonnement</t>
+  </si>
+  <si>
+    <t>Pas de marge maximum</t>
+  </si>
+  <si>
+    <t>Gaz= Cas par cas</t>
+  </si>
+  <si>
+    <t>Gaz= 
+20 €/MWh si &lt; 1 GWh
+10 €/MWh si &gt; 1 GWh et &lt; 5 GWh
+5 €/MWh si &gt; 5 GWh</t>
+  </si>
+  <si>
+    <t>Electricité= 30 €/MWh</t>
+  </si>
+  <si>
+    <t>Electricité et Gaz= Grille si C5  / Si GC= 
+20 €/MWh &lt; 1 GWh
+15 €/MWh &lt; 10 GWh
+10 €/MWh &lt; 20 GWh
+6 €/MWh &lt; 80 GWh
+4 €/MWh &gt; 80 GWh</t>
+  </si>
+  <si>
+    <t>Electricité et Gaz= 60€/MWh pour MID et 25€/MWh pour GC</t>
+  </si>
+  <si>
+    <t>Electricité et Gaz= 25€/MWh</t>
+  </si>
+  <si>
+    <t>Electricité et Gaz= Pas de limite de marge</t>
+  </si>
+  <si>
+    <t>Gaz= 18€/MWh</t>
+  </si>
+  <si>
+    <t>Electricité et Gaz= 30€/MWh</t>
+  </si>
+  <si>
+    <t>Electricité= 40€/MWh GAZ= 20€/MWh</t>
+  </si>
+  <si>
+    <t>Electricité= 25€/MWh</t>
+  </si>
+  <si>
+    <t>Electricité et Gaz= 6€/MWh</t>
+  </si>
+  <si>
+    <t>Electricité et Gaz= 140 €/PRM</t>
+  </si>
+  <si>
+    <t>Electricité=
+C5 : 20 €/MWh 
+C4 : 15 €/MWh
+C2 : 10 €/MWh  / Gaz= T2 : 15 €/MWh 
+T3 : 10 €/MWh</t>
+  </si>
+  <si>
+    <t>Electricité = 20 €/MWh &lt; 500 MWh
+15 €/MWh &lt; 3 GWh
+10 €/MWh &gt; 3 GWh</t>
+  </si>
+  <si>
+    <t>Electricité et Gaz= Grille</t>
+  </si>
+  <si>
+    <t>Electricité= &lt; 100 MWh/an : 25 €/MWh
+&gt; 100 MWh/an : 20 €/MWh</t>
   </si>
 </sst>
 </file>
@@ -786,7 +918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -838,6 +970,9 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -873,8 +1008,11 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1212,49 +1350,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="30" width="18" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" customWidth="1"/>
+    <col min="6" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18" customWidth="1"/>
+    <col min="24" max="24" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="30" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-    </row>
-    <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:30" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+    </row>
+    <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:30" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1346,8 +1490,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+    <row r="4" spans="1:30" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="30" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1436,8 +1580,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22"/>
+    <row r="5" spans="1:30" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23"/>
       <c r="B5" s="2" t="s">
         <v>36</v>
       </c>
@@ -1524,8 +1668,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
+    <row r="6" spans="1:30" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23"/>
       <c r="B6" s="2" t="s">
         <v>37</v>
       </c>
@@ -1612,8 +1756,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
+    <row r="7" spans="1:30" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="23"/>
       <c r="B7" s="2" t="s">
         <v>38</v>
       </c>
@@ -1700,8 +1844,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23"/>
+    <row r="8" spans="1:30" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="24"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
@@ -1780,8 +1924,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:30" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -1862,8 +2006,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22"/>
+    <row r="10" spans="1:30" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="23"/>
       <c r="B10" s="7" t="s">
         <v>47</v>
       </c>
@@ -1950,8 +2094,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22"/>
+    <row r="11" spans="1:30" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="23"/>
       <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
@@ -2036,8 +2180,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
+    <row r="12" spans="1:30" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="24"/>
       <c r="B12" s="7" t="s">
         <v>50</v>
       </c>
@@ -2124,12 +2268,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="9">
         <v>2029</v>
       </c>
@@ -2204,12 +2348,12 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="9">
         <v>2029</v>
       </c>
@@ -2280,12 +2424,12 @@
       <c r="AC14" s="9"/>
       <c r="AD14" s="9"/>
     </row>
-    <row r="15" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="27"/>
       <c r="D15" s="9" t="s">
         <v>55</v>
       </c>
@@ -2368,12 +2512,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:30" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="9" t="s">
         <v>68</v>
       </c>
@@ -2386,10 +2530,10 @@
       <c r="G16" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H16" s="34" t="s">
+      <c r="H16" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="I16" s="19" t="s">
         <v>153</v>
       </c>
       <c r="J16" s="9" t="s">
@@ -2413,7 +2557,7 @@
       <c r="P16" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="Q16" s="34" t="s">
+      <c r="Q16" s="19" t="s">
         <v>153</v>
       </c>
       <c r="R16" s="9" t="s">
@@ -2456,12 +2600,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+    <row r="17" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="27"/>
       <c r="D17" s="9" t="s">
         <v>84</v>
       </c>
@@ -2544,12 +2688,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+    <row r="18" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
       <c r="D18" s="9" t="s">
         <v>101</v>
       </c>
@@ -2632,12 +2776,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:30" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
       <c r="D19" s="9" t="s">
         <v>101</v>
       </c>
@@ -2720,12 +2864,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+    <row r="20" spans="1:30" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="27"/>
       <c r="D20" s="9" t="s">
         <v>113</v>
       </c>
@@ -2808,12 +2952,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+    <row r="21" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="30"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="31"/>
       <c r="D21" s="17" t="s">
         <v>33</v>
       </c>
@@ -2896,17 +3040,17 @@
         <v>143</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="31"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A22" s="32"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
       <c r="D23" s="18" t="s">
         <v>145</v>
       </c>
@@ -2989,11 +3133,97 @@
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="L24" s="13"/>
+    <row r="24" spans="1:30" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="K24" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="M24" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="N24" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="O24" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="P24" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q24" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="R24" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="S24" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="T24" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="U24" t="s">
+        <v>172</v>
+      </c>
+      <c r="V24" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="W24" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="X24" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y24" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z24" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA24" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC24" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD24" s="36" t="s">
+        <v>180</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="A14:C14"/>
@@ -3016,15 +3246,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26205596-00C2-47DD-8F92-E7A8610DE83C}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.140625" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.109375" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>129</v>
       </c>
@@ -3032,7 +3262,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A2" s="12" t="s">
         <v>20</v>
       </c>
@@ -3040,7 +3270,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A3" s="12" t="s">
         <v>26</v>
       </c>
@@ -3048,7 +3278,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A4" s="12" t="s">
         <v>18</v>
       </c>
@@ -3056,7 +3286,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A5" s="12" t="s">
         <v>21</v>
       </c>
@@ -3064,7 +3294,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -3072,7 +3302,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A7" s="12" t="s">
         <v>119</v>
       </c>
@@ -3080,7 +3310,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A8" s="12" t="s">
         <v>4</v>
       </c>
@@ -3088,7 +3318,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A9" s="12" t="s">
         <v>120</v>
       </c>
@@ -3096,7 +3326,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A10" s="12" t="s">
         <v>14</v>
       </c>
@@ -3104,7 +3334,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A11" s="12" t="s">
         <v>10</v>
       </c>
@@ -3112,7 +3342,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
@@ -3120,7 +3350,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A13" s="12" t="s">
         <v>23</v>
       </c>
@@ -3128,7 +3358,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A14" s="12" t="s">
         <v>7</v>
       </c>
@@ -3136,7 +3366,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A15" s="12" t="s">
         <v>27</v>
       </c>
@@ -3144,7 +3374,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A16" s="14" t="s">
         <v>5</v>
       </c>
@@ -3152,7 +3382,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A17" s="14" t="s">
         <v>24</v>
       </c>
@@ -3160,7 +3390,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A18" s="14" t="s">
         <v>9</v>
       </c>
@@ -3168,7 +3398,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A19" s="14" t="s">
         <v>30</v>
       </c>
@@ -3176,7 +3406,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A20" s="14" t="s">
         <v>12</v>
       </c>
@@ -3184,7 +3414,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A21" s="14" t="s">
         <v>121</v>
       </c>
@@ -3192,7 +3422,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A22" s="15" t="s">
         <v>25</v>
       </c>
@@ -3200,7 +3430,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A23" s="15" t="s">
         <v>29</v>
       </c>
@@ -3208,7 +3438,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A24" s="15" t="s">
         <v>19</v>
       </c>
@@ -3216,7 +3446,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A25" s="15" t="s">
         <v>13</v>
       </c>
@@ -3224,7 +3454,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A26" s="15" t="s">
         <v>22</v>
       </c>
@@ -3232,7 +3462,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A27" s="16" t="s">
         <v>8</v>
       </c>
@@ -3240,7 +3470,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A28" s="16" t="s">
         <v>122</v>
       </c>
@@ -3248,7 +3478,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A29" s="16" t="s">
         <v>17</v>
       </c>
@@ -3256,7 +3486,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A30" s="16" t="s">
         <v>123</v>
       </c>
@@ -3264,7 +3494,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="21.75" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A31" s="10"/>
     </row>
   </sheetData>
